--- a/Final_results/PerformanceVNS.xlsx
+++ b/Final_results/PerformanceVNS.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://enstafr-my.sharepoint.com/personal/christopher_tsa_ensta-paris_fr/Documents/ENSTA/3A/Metaheuristique/project/final_results/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9B64BC59-8E25-EC4C-8220-64D3F56FFE3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="8_{9B64BC59-8E25-EC4C-8220-64D3F56FFE3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FBAABC18-575F-884D-B716-F1A019FEE10C}"/>
   <bookViews>
-    <workbookView xWindow="30580" yWindow="-8660" windowWidth="27240" windowHeight="15940" xr2:uid="{D4557CCB-A576-0348-A72A-41406F20CB7C}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{D4557CCB-A576-0348-A72A-41406F20CB7C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -722,17 +722,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1071,7 +1072,8 @@
   <dimension ref="A1:H103"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="4" width="18.5" customWidth="1"/>
+    <col min="3" max="3" width="18.5" customWidth="1"/>
+    <col min="4" max="4" width="18.5" style="8" customWidth="1"/>
     <col min="5" max="5" width="17.5" customWidth="1"/>
     <col min="6" max="6" width="21.5" customWidth="1"/>
     <col min="7" max="7" width="21.83203125" customWidth="1"/>
@@ -1088,7 +1090,7 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="8" t="s">
         <v>3</v>
       </c>
       <c r="E1" t="s">
@@ -1114,7 +1116,7 @@
       <c r="C2">
         <v>100</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="8">
         <v>5</v>
       </c>
       <c r="E2" t="s">
@@ -1140,7 +1142,7 @@
       <c r="C3">
         <v>100</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="8">
         <v>5</v>
       </c>
       <c r="E3" t="s">
@@ -1166,7 +1168,7 @@
       <c r="C4">
         <v>100</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="8">
         <v>5</v>
       </c>
       <c r="E4" t="s">
@@ -1192,7 +1194,7 @@
       <c r="C5">
         <v>100</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="8">
         <v>5</v>
       </c>
       <c r="E5" t="s">
@@ -1218,7 +1220,7 @@
       <c r="C6">
         <v>100</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="8">
         <v>5</v>
       </c>
       <c r="E6" t="s">
@@ -1244,7 +1246,7 @@
       <c r="C7">
         <v>100</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="8">
         <v>5</v>
       </c>
       <c r="E7" t="s">
@@ -1270,7 +1272,7 @@
       <c r="C8">
         <v>100</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="8">
         <v>5</v>
       </c>
       <c r="E8" t="s">
@@ -1296,7 +1298,7 @@
       <c r="C9">
         <v>100</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="8">
         <v>5</v>
       </c>
       <c r="E9" t="s">
@@ -1322,7 +1324,7 @@
       <c r="C10">
         <v>100</v>
       </c>
-      <c r="D10">
+      <c r="D10" s="8">
         <v>5</v>
       </c>
       <c r="E10" t="s">
@@ -1348,7 +1350,7 @@
       <c r="C11">
         <v>100</v>
       </c>
-      <c r="D11">
+      <c r="D11" s="8">
         <v>5</v>
       </c>
       <c r="E11" t="s">
@@ -1374,7 +1376,7 @@
       <c r="C12">
         <v>250</v>
       </c>
-      <c r="D12">
+      <c r="D12" s="8">
         <v>5</v>
       </c>
       <c r="E12" t="s">
@@ -1400,7 +1402,7 @@
       <c r="C13">
         <v>250</v>
       </c>
-      <c r="D13">
+      <c r="D13" s="8">
         <v>5</v>
       </c>
       <c r="E13" t="s">
@@ -1426,7 +1428,7 @@
       <c r="C14">
         <v>250</v>
       </c>
-      <c r="D14">
+      <c r="D14" s="8">
         <v>5</v>
       </c>
       <c r="E14" t="s">
@@ -1452,7 +1454,7 @@
       <c r="C15">
         <v>250</v>
       </c>
-      <c r="D15">
+      <c r="D15" s="8">
         <v>5</v>
       </c>
       <c r="E15" t="s">
@@ -1478,7 +1480,7 @@
       <c r="C16">
         <v>250</v>
       </c>
-      <c r="D16">
+      <c r="D16" s="8">
         <v>5</v>
       </c>
       <c r="E16" t="s">
@@ -1504,7 +1506,7 @@
       <c r="C17">
         <v>250</v>
       </c>
-      <c r="D17">
+      <c r="D17" s="8">
         <v>5</v>
       </c>
       <c r="E17" t="s">
@@ -1530,7 +1532,7 @@
       <c r="C18">
         <v>250</v>
       </c>
-      <c r="D18">
+      <c r="D18" s="8">
         <v>5</v>
       </c>
       <c r="E18" t="s">
@@ -1556,7 +1558,7 @@
       <c r="C19">
         <v>250</v>
       </c>
-      <c r="D19">
+      <c r="D19" s="8">
         <v>5</v>
       </c>
       <c r="E19" t="s">
@@ -1582,7 +1584,7 @@
       <c r="C20">
         <v>250</v>
       </c>
-      <c r="D20">
+      <c r="D20" s="8">
         <v>5</v>
       </c>
       <c r="E20" t="s">
@@ -1608,7 +1610,7 @@
       <c r="C21">
         <v>250</v>
       </c>
-      <c r="D21">
+      <c r="D21" s="8">
         <v>5</v>
       </c>
       <c r="E21" t="s">
@@ -1634,7 +1636,7 @@
       <c r="C22">
         <v>500</v>
       </c>
-      <c r="D22">
+      <c r="D22" s="8">
         <v>5</v>
       </c>
       <c r="E22" t="s">
@@ -1660,7 +1662,7 @@
       <c r="C23">
         <v>500</v>
       </c>
-      <c r="D23">
+      <c r="D23" s="8">
         <v>5</v>
       </c>
       <c r="E23" t="s">
@@ -1686,7 +1688,7 @@
       <c r="C24">
         <v>500</v>
       </c>
-      <c r="D24">
+      <c r="D24" s="8">
         <v>5</v>
       </c>
       <c r="E24" t="s">
@@ -1712,7 +1714,7 @@
       <c r="C25">
         <v>500</v>
       </c>
-      <c r="D25">
+      <c r="D25" s="8">
         <v>5</v>
       </c>
       <c r="E25" t="s">
@@ -1738,7 +1740,7 @@
       <c r="C26">
         <v>500</v>
       </c>
-      <c r="D26">
+      <c r="D26" s="8">
         <v>5</v>
       </c>
       <c r="E26" t="s">
@@ -1764,7 +1766,7 @@
       <c r="C27">
         <v>500</v>
       </c>
-      <c r="D27">
+      <c r="D27" s="8">
         <v>5</v>
       </c>
       <c r="E27" t="s">
@@ -1790,7 +1792,7 @@
       <c r="C28">
         <v>500</v>
       </c>
-      <c r="D28">
+      <c r="D28" s="8">
         <v>5</v>
       </c>
       <c r="E28" t="s">
@@ -1816,7 +1818,7 @@
       <c r="C29">
         <v>500</v>
       </c>
-      <c r="D29">
+      <c r="D29" s="8">
         <v>5</v>
       </c>
       <c r="E29" t="s">
@@ -1842,7 +1844,7 @@
       <c r="C30">
         <v>500</v>
       </c>
-      <c r="D30">
+      <c r="D30" s="8">
         <v>5</v>
       </c>
       <c r="E30" t="s">
@@ -1868,7 +1870,7 @@
       <c r="C31">
         <v>500</v>
       </c>
-      <c r="D31">
+      <c r="D31" s="8">
         <v>5</v>
       </c>
       <c r="E31" t="s">
@@ -1894,7 +1896,7 @@
       <c r="C32">
         <v>100</v>
       </c>
-      <c r="D32">
+      <c r="D32" s="8">
         <v>10</v>
       </c>
       <c r="E32" t="s">
@@ -1920,7 +1922,7 @@
       <c r="C33">
         <v>100</v>
       </c>
-      <c r="D33">
+      <c r="D33" s="8">
         <v>10</v>
       </c>
       <c r="E33" t="s">
@@ -1946,7 +1948,7 @@
       <c r="C34">
         <v>100</v>
       </c>
-      <c r="D34">
+      <c r="D34" s="8">
         <v>10</v>
       </c>
       <c r="E34" t="s">
@@ -1972,7 +1974,7 @@
       <c r="C35">
         <v>100</v>
       </c>
-      <c r="D35">
+      <c r="D35" s="8">
         <v>10</v>
       </c>
       <c r="E35" t="s">
@@ -1998,7 +2000,7 @@
       <c r="C36">
         <v>100</v>
       </c>
-      <c r="D36">
+      <c r="D36" s="8">
         <v>10</v>
       </c>
       <c r="E36" t="s">
@@ -2024,7 +2026,7 @@
       <c r="C37">
         <v>100</v>
       </c>
-      <c r="D37">
+      <c r="D37" s="8">
         <v>10</v>
       </c>
       <c r="E37" t="s">
@@ -2050,7 +2052,7 @@
       <c r="C38">
         <v>100</v>
       </c>
-      <c r="D38">
+      <c r="D38" s="8">
         <v>10</v>
       </c>
       <c r="E38" t="s">
@@ -2076,7 +2078,7 @@
       <c r="C39">
         <v>100</v>
       </c>
-      <c r="D39">
+      <c r="D39" s="8">
         <v>10</v>
       </c>
       <c r="E39" t="s">
@@ -2102,7 +2104,7 @@
       <c r="C40">
         <v>100</v>
       </c>
-      <c r="D40">
+      <c r="D40" s="8">
         <v>10</v>
       </c>
       <c r="E40" t="s">
@@ -2128,7 +2130,7 @@
       <c r="C41">
         <v>100</v>
       </c>
-      <c r="D41">
+      <c r="D41" s="8">
         <v>10</v>
       </c>
       <c r="E41" t="s">
@@ -2154,7 +2156,7 @@
       <c r="C42">
         <v>250</v>
       </c>
-      <c r="D42">
+      <c r="D42" s="8">
         <v>10</v>
       </c>
       <c r="E42" t="s">
@@ -2180,7 +2182,7 @@
       <c r="C43">
         <v>250</v>
       </c>
-      <c r="D43">
+      <c r="D43" s="8">
         <v>10</v>
       </c>
       <c r="E43" t="s">
@@ -2206,7 +2208,7 @@
       <c r="C44">
         <v>250</v>
       </c>
-      <c r="D44">
+      <c r="D44" s="8">
         <v>10</v>
       </c>
       <c r="E44" t="s">
@@ -2232,7 +2234,7 @@
       <c r="C45">
         <v>250</v>
       </c>
-      <c r="D45">
+      <c r="D45" s="8">
         <v>10</v>
       </c>
       <c r="E45" t="s">
@@ -2258,7 +2260,7 @@
       <c r="C46">
         <v>250</v>
       </c>
-      <c r="D46">
+      <c r="D46" s="8">
         <v>10</v>
       </c>
       <c r="E46" t="s">
@@ -2284,7 +2286,7 @@
       <c r="C47">
         <v>250</v>
       </c>
-      <c r="D47">
+      <c r="D47" s="8">
         <v>10</v>
       </c>
       <c r="E47" t="s">
@@ -2310,7 +2312,7 @@
       <c r="C48">
         <v>250</v>
       </c>
-      <c r="D48">
+      <c r="D48" s="8">
         <v>10</v>
       </c>
       <c r="E48" t="s">
@@ -2336,7 +2338,7 @@
       <c r="C49">
         <v>250</v>
       </c>
-      <c r="D49">
+      <c r="D49" s="8">
         <v>10</v>
       </c>
       <c r="E49" t="s">
@@ -2362,7 +2364,7 @@
       <c r="C50">
         <v>250</v>
       </c>
-      <c r="D50">
+      <c r="D50" s="8">
         <v>10</v>
       </c>
       <c r="E50" t="s">
@@ -2388,7 +2390,7 @@
       <c r="C51">
         <v>250</v>
       </c>
-      <c r="D51">
+      <c r="D51" s="8">
         <v>10</v>
       </c>
       <c r="E51" t="s">
@@ -2414,7 +2416,7 @@
       <c r="C52">
         <v>500</v>
       </c>
-      <c r="D52">
+      <c r="D52" s="8">
         <v>10</v>
       </c>
       <c r="E52" t="s">
@@ -2440,7 +2442,7 @@
       <c r="C53">
         <v>500</v>
       </c>
-      <c r="D53">
+      <c r="D53" s="8">
         <v>10</v>
       </c>
       <c r="E53" t="s">
@@ -2466,7 +2468,7 @@
       <c r="C54">
         <v>500</v>
       </c>
-      <c r="D54">
+      <c r="D54" s="8">
         <v>10</v>
       </c>
       <c r="E54" t="s">
@@ -2492,7 +2494,7 @@
       <c r="C55">
         <v>500</v>
       </c>
-      <c r="D55">
+      <c r="D55" s="8">
         <v>10</v>
       </c>
       <c r="E55" t="s">
@@ -2518,7 +2520,7 @@
       <c r="C56">
         <v>500</v>
       </c>
-      <c r="D56">
+      <c r="D56" s="8">
         <v>10</v>
       </c>
       <c r="E56" t="s">
@@ -2544,7 +2546,7 @@
       <c r="C57">
         <v>500</v>
       </c>
-      <c r="D57">
+      <c r="D57" s="8">
         <v>10</v>
       </c>
       <c r="E57" t="s">
@@ -2570,7 +2572,7 @@
       <c r="C58">
         <v>500</v>
       </c>
-      <c r="D58">
+      <c r="D58" s="8">
         <v>10</v>
       </c>
       <c r="E58" t="s">
@@ -2596,7 +2598,7 @@
       <c r="C59">
         <v>500</v>
       </c>
-      <c r="D59">
+      <c r="D59" s="8">
         <v>10</v>
       </c>
       <c r="E59" t="s">
@@ -2622,7 +2624,7 @@
       <c r="C60">
         <v>500</v>
       </c>
-      <c r="D60">
+      <c r="D60" s="8">
         <v>10</v>
       </c>
       <c r="E60" t="s">
@@ -2648,7 +2650,7 @@
       <c r="C61">
         <v>500</v>
       </c>
-      <c r="D61">
+      <c r="D61" s="8">
         <v>10</v>
       </c>
       <c r="E61" t="s">
@@ -2674,7 +2676,7 @@
       <c r="C62">
         <v>100</v>
       </c>
-      <c r="D62">
+      <c r="D62" s="8">
         <v>30</v>
       </c>
       <c r="E62" t="s">
@@ -2700,7 +2702,7 @@
       <c r="C63">
         <v>100</v>
       </c>
-      <c r="D63">
+      <c r="D63" s="8">
         <v>30</v>
       </c>
       <c r="E63" t="s">
@@ -2726,7 +2728,7 @@
       <c r="C64">
         <v>100</v>
       </c>
-      <c r="D64">
+      <c r="D64" s="8">
         <v>30</v>
       </c>
       <c r="E64" t="s">
@@ -2752,7 +2754,7 @@
       <c r="C65">
         <v>100</v>
       </c>
-      <c r="D65">
+      <c r="D65" s="8">
         <v>30</v>
       </c>
       <c r="E65" t="s">
@@ -2778,7 +2780,7 @@
       <c r="C66">
         <v>100</v>
       </c>
-      <c r="D66">
+      <c r="D66" s="8">
         <v>30</v>
       </c>
       <c r="E66" t="s">
@@ -2804,7 +2806,7 @@
       <c r="C67">
         <v>100</v>
       </c>
-      <c r="D67">
+      <c r="D67" s="8">
         <v>30</v>
       </c>
       <c r="E67" t="s">
@@ -2830,7 +2832,7 @@
       <c r="C68">
         <v>100</v>
       </c>
-      <c r="D68">
+      <c r="D68" s="8">
         <v>30</v>
       </c>
       <c r="E68" t="s">
@@ -2856,7 +2858,7 @@
       <c r="C69">
         <v>100</v>
       </c>
-      <c r="D69">
+      <c r="D69" s="8">
         <v>30</v>
       </c>
       <c r="E69" t="s">
@@ -2882,7 +2884,7 @@
       <c r="C70">
         <v>100</v>
       </c>
-      <c r="D70">
+      <c r="D70" s="8">
         <v>30</v>
       </c>
       <c r="E70" t="s">
@@ -2908,7 +2910,7 @@
       <c r="C71">
         <v>100</v>
       </c>
-      <c r="D71">
+      <c r="D71" s="8">
         <v>30</v>
       </c>
       <c r="E71" t="s">
@@ -2934,7 +2936,7 @@
       <c r="C72">
         <v>250</v>
       </c>
-      <c r="D72">
+      <c r="D72" s="8">
         <v>30</v>
       </c>
       <c r="E72" t="s">
@@ -2960,7 +2962,7 @@
       <c r="C73">
         <v>250</v>
       </c>
-      <c r="D73">
+      <c r="D73" s="8">
         <v>30</v>
       </c>
       <c r="E73" t="s">
@@ -2986,7 +2988,7 @@
       <c r="C74">
         <v>250</v>
       </c>
-      <c r="D74">
+      <c r="D74" s="8">
         <v>30</v>
       </c>
       <c r="E74" t="s">
@@ -3012,7 +3014,7 @@
       <c r="C75">
         <v>250</v>
       </c>
-      <c r="D75">
+      <c r="D75" s="8">
         <v>30</v>
       </c>
       <c r="E75" t="s">
@@ -3038,7 +3040,7 @@
       <c r="C76">
         <v>250</v>
       </c>
-      <c r="D76">
+      <c r="D76" s="8">
         <v>30</v>
       </c>
       <c r="E76" t="s">
@@ -3064,7 +3066,7 @@
       <c r="C77">
         <v>250</v>
       </c>
-      <c r="D77">
+      <c r="D77" s="8">
         <v>30</v>
       </c>
       <c r="E77" t="s">
@@ -3090,7 +3092,7 @@
       <c r="C78">
         <v>250</v>
       </c>
-      <c r="D78">
+      <c r="D78" s="8">
         <v>30</v>
       </c>
       <c r="E78" t="s">
@@ -3116,7 +3118,7 @@
       <c r="C79">
         <v>250</v>
       </c>
-      <c r="D79">
+      <c r="D79" s="8">
         <v>30</v>
       </c>
       <c r="E79" t="s">
@@ -3142,7 +3144,7 @@
       <c r="C80">
         <v>250</v>
       </c>
-      <c r="D80">
+      <c r="D80" s="8">
         <v>30</v>
       </c>
       <c r="E80" t="s">
@@ -3168,7 +3170,7 @@
       <c r="C81">
         <v>250</v>
       </c>
-      <c r="D81">
+      <c r="D81" s="8">
         <v>30</v>
       </c>
       <c r="E81" t="s">
@@ -3194,7 +3196,7 @@
       <c r="C82">
         <v>500</v>
       </c>
-      <c r="D82">
+      <c r="D82" s="8">
         <v>30</v>
       </c>
       <c r="E82" t="s">
@@ -3220,7 +3222,7 @@
       <c r="C83">
         <v>500</v>
       </c>
-      <c r="D83">
+      <c r="D83" s="8">
         <v>30</v>
       </c>
       <c r="E83" t="s">
@@ -3246,7 +3248,7 @@
       <c r="C84">
         <v>500</v>
       </c>
-      <c r="D84">
+      <c r="D84" s="8">
         <v>30</v>
       </c>
       <c r="E84" t="s">
@@ -3272,7 +3274,7 @@
       <c r="C85">
         <v>500</v>
       </c>
-      <c r="D85">
+      <c r="D85" s="8">
         <v>30</v>
       </c>
       <c r="E85" t="s">
@@ -3298,7 +3300,7 @@
       <c r="C86">
         <v>500</v>
       </c>
-      <c r="D86">
+      <c r="D86" s="8">
         <v>30</v>
       </c>
       <c r="E86" t="s">
@@ -3324,7 +3326,7 @@
       <c r="C87">
         <v>500</v>
       </c>
-      <c r="D87">
+      <c r="D87" s="8">
         <v>30</v>
       </c>
       <c r="E87" t="s">
@@ -3350,7 +3352,7 @@
       <c r="C88">
         <v>500</v>
       </c>
-      <c r="D88">
+      <c r="D88" s="8">
         <v>30</v>
       </c>
       <c r="E88" t="s">
@@ -3376,7 +3378,7 @@
       <c r="C89">
         <v>500</v>
       </c>
-      <c r="D89">
+      <c r="D89" s="8">
         <v>30</v>
       </c>
       <c r="E89" t="s">
@@ -3402,7 +3404,7 @@
       <c r="C90">
         <v>500</v>
       </c>
-      <c r="D90">
+      <c r="D90" s="8">
         <v>30</v>
       </c>
       <c r="E90" t="s">
@@ -3428,7 +3430,7 @@
       <c r="C91">
         <v>500</v>
       </c>
-      <c r="D91">
+      <c r="D91" s="8">
         <v>30</v>
       </c>
       <c r="E91" t="s">
@@ -3448,7 +3450,7 @@
       <c r="C99" s="4" t="s">
         <v>193</v>
       </c>
-      <c r="D99" s="4" t="s">
+      <c r="D99" s="9" t="s">
         <v>199</v>
       </c>
       <c r="E99" s="4" t="s">
@@ -3456,53 +3458,53 @@
       </c>
     </row>
     <row r="100" spans="3:5" x14ac:dyDescent="0.2">
-      <c r="C100" s="9" t="s">
+      <c r="C100" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="D100" s="5">
+      <c r="D100" s="10">
         <f>MIN(G2:G91)</f>
         <v>1.1889091758311701E-3</v>
       </c>
-      <c r="E100" s="6">
+      <c r="E100" s="5">
         <f>MIN(H2:H91)</f>
         <v>60.000055074691701</v>
       </c>
     </row>
     <row r="101" spans="3:5" x14ac:dyDescent="0.2">
-      <c r="C101" s="9" t="s">
+      <c r="C101" s="7" t="s">
         <v>195</v>
       </c>
-      <c r="D101" s="5">
+      <c r="D101" s="10">
         <f>MAX(G2:G91)</f>
         <v>7.5888745625345297E-2</v>
       </c>
-      <c r="E101" s="7">
+      <c r="E101" s="6">
         <f>MAX(H2:H91)</f>
         <v>168.54808115959099</v>
       </c>
     </row>
     <row r="102" spans="3:5" x14ac:dyDescent="0.2">
-      <c r="C102" s="9" t="s">
+      <c r="C102" s="7" t="s">
         <v>196</v>
       </c>
-      <c r="D102" s="5">
+      <c r="D102" s="10">
         <f>AVERAGE(G2:G91)</f>
         <v>1.7225185382667069E-2</v>
       </c>
-      <c r="E102" s="7">
+      <c r="E102" s="6">
         <f>AVERAGE(H2:H91)</f>
         <v>61.673892288737804</v>
       </c>
     </row>
     <row r="103" spans="3:5" x14ac:dyDescent="0.2">
-      <c r="C103" s="9" t="s">
+      <c r="C103" s="7" t="s">
         <v>197</v>
       </c>
-      <c r="D103" s="8">
+      <c r="D103" s="10">
         <f>STDEV(G2:G91)</f>
         <v>1.2564988786500643E-2</v>
       </c>
-      <c r="E103" s="6">
+      <c r="E103" s="5">
         <f>STDEV(H2:H91)</f>
         <v>11.416891214611033</v>
       </c>
